--- a/public/Motors.xlsx
+++ b/public/Motors.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="226">
   <si>
     <t>name</t>
   </si>
@@ -690,6 +690,18 @@
   </si>
   <si>
     <t>N_d</t>
+  </si>
+  <si>
+    <t>mot_pic</t>
+  </si>
+  <si>
+    <t>https://smarta.ru/upload/iblock/7e6/s7ux3cbdzbpaw5w5ec0jax8tlb8ypfgv/EMMR_AS_BC_P_small_1.png</t>
+  </si>
+  <si>
+    <t>https://smarta.ru/upload/iblock/626/setjqkjevv8wqwc18qtalpo8e1dqg077/EMMR_AS_BC_big_1.png</t>
+  </si>
+  <si>
+    <t>https://smarta.ru/upload/iblock/fe7/ryifndfl23l64v8i1dvojliur5avjydh/EMMR_AS_A_1.png</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J213"/>
+  <dimension ref="A1:K213"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
@@ -1017,7 +1029,7 @@
     <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1048,8 +1060,11 @@
       <c r="J1" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1080,8 +1095,11 @@
       <c r="J2">
         <v>3000</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1130,11 @@
       <c r="J3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1144,8 +1165,11 @@
       <c r="J4">
         <v>3000</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1176,8 +1200,11 @@
       <c r="J5">
         <v>3000</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1208,8 +1235,11 @@
       <c r="J6">
         <v>3000</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1240,8 +1270,11 @@
       <c r="J7">
         <v>3000</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1272,8 +1305,11 @@
       <c r="J8">
         <v>3000</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1304,8 +1340,11 @@
       <c r="J9">
         <v>3000</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1336,8 +1375,11 @@
       <c r="J10">
         <v>3000</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1368,8 +1410,11 @@
       <c r="J11">
         <v>3000</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1400,8 +1445,11 @@
       <c r="J12">
         <v>1500</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1432,8 +1480,11 @@
       <c r="J13">
         <v>1500</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1464,8 +1515,11 @@
       <c r="J14">
         <v>1500</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1496,8 +1550,11 @@
       <c r="J15">
         <v>1500</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1528,8 +1585,11 @@
       <c r="J16">
         <v>1500</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1560,8 +1620,11 @@
       <c r="J17">
         <v>1500</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1592,8 +1655,11 @@
       <c r="J18">
         <v>2500</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1624,8 +1690,11 @@
       <c r="J19">
         <v>2500</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1656,8 +1725,11 @@
       <c r="J20">
         <v>2500</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1688,8 +1760,11 @@
       <c r="J21">
         <v>2500</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1720,8 +1795,11 @@
       <c r="J22">
         <v>2500</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1752,8 +1830,11 @@
       <c r="J23">
         <v>2500</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1784,8 +1865,11 @@
       <c r="J24">
         <v>2500</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1816,8 +1900,11 @@
       <c r="J25">
         <v>2500</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1848,8 +1935,11 @@
       <c r="J26">
         <v>2500</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1880,8 +1970,11 @@
       <c r="J27">
         <v>2500</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1912,8 +2005,11 @@
       <c r="J28">
         <v>1500</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1944,8 +2040,11 @@
       <c r="J29">
         <v>1500</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1976,8 +2075,11 @@
       <c r="J30">
         <v>2000</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -2008,8 +2110,11 @@
       <c r="J31">
         <v>2000</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -2040,8 +2145,11 @@
       <c r="J32">
         <v>1500</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -2072,8 +2180,11 @@
       <c r="J33">
         <v>1500</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -2104,8 +2215,11 @@
       <c r="J34">
         <v>1500</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -2136,8 +2250,11 @@
       <c r="J35">
         <v>1500</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -2168,8 +2285,11 @@
       <c r="J36">
         <v>2000</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -2200,8 +2320,11 @@
       <c r="J37">
         <v>4000</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -2232,8 +2355,11 @@
       <c r="J38">
         <v>2000</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -2264,8 +2390,11 @@
       <c r="J39">
         <v>4000</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -2296,8 +2425,11 @@
       <c r="J40">
         <v>5800</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -2328,8 +2460,11 @@
       <c r="J41">
         <v>10000</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -2360,8 +2495,11 @@
       <c r="J42">
         <v>5800</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -2392,8 +2530,11 @@
       <c r="J43">
         <v>10000</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -2424,8 +2565,11 @@
       <c r="J44">
         <v>1700</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -2456,8 +2600,11 @@
       <c r="J45">
         <v>4400</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -2488,8 +2635,11 @@
       <c r="J46">
         <v>1700</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -2520,8 +2670,11 @@
       <c r="J47">
         <v>4400</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -2552,8 +2705,11 @@
       <c r="J48">
         <v>4600</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -2584,8 +2740,11 @@
       <c r="J49">
         <v>5900</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -2616,8 +2775,11 @@
       <c r="J50">
         <v>4600</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -2648,8 +2810,11 @@
       <c r="J51">
         <v>5900</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -2680,8 +2845,11 @@
       <c r="J52">
         <v>1400</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K52" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -2712,8 +2880,11 @@
       <c r="J53">
         <v>3000</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K53" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2744,8 +2915,11 @@
       <c r="J54">
         <v>1400</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K54" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -2776,8 +2950,11 @@
       <c r="J55">
         <v>3000</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -2808,8 +2985,11 @@
       <c r="J56">
         <v>4200</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K56" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -2840,8 +3020,11 @@
       <c r="J57">
         <v>5900</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K57" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -2872,8 +3055,11 @@
       <c r="J58">
         <v>4200</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K58" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -2904,8 +3090,11 @@
       <c r="J59">
         <v>5900</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K59" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -2936,8 +3125,11 @@
       <c r="J60">
         <v>1750</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -2968,8 +3160,11 @@
       <c r="J61">
         <v>3100</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K61" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -3000,8 +3195,11 @@
       <c r="J62">
         <v>1750</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K62" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -3032,8 +3230,11 @@
       <c r="J63">
         <v>3100</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K63" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -3064,8 +3265,11 @@
       <c r="J64">
         <v>1750</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K64" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -3096,8 +3300,11 @@
       <c r="J65">
         <v>5200</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K65" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -3128,8 +3335,11 @@
       <c r="J66">
         <v>1750</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K66" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -3160,8 +3370,11 @@
       <c r="J67">
         <v>5200</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K67" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -3192,8 +3405,11 @@
       <c r="J68">
         <v>1600</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K68" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -3224,8 +3440,11 @@
       <c r="J69">
         <v>3000</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K69" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -3256,8 +3475,11 @@
       <c r="J70">
         <v>1600</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K70" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -3288,8 +3510,11 @@
       <c r="J71">
         <v>3000</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K71" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -3320,8 +3545,11 @@
       <c r="J72">
         <v>1600</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K72" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -3352,8 +3580,11 @@
       <c r="J73">
         <v>3900</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K73" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -3384,8 +3615,11 @@
       <c r="J74">
         <v>1600</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K74" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -3416,8 +3650,11 @@
       <c r="J75">
         <v>3900</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K75" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -3448,8 +3685,11 @@
       <c r="J76">
         <v>1600</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K76" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -3480,8 +3720,11 @@
       <c r="J77">
         <v>2450</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K77" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -3512,8 +3755,11 @@
       <c r="J78">
         <v>1600</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K78" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>86</v>
       </c>
@@ -3544,8 +3790,11 @@
       <c r="J79">
         <v>2450</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K79" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>87</v>
       </c>
@@ -3576,8 +3825,11 @@
       <c r="J80">
         <v>1800</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K80" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>88</v>
       </c>
@@ -3608,8 +3860,11 @@
       <c r="J81">
         <v>3800</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K81" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>89</v>
       </c>
@@ -3640,8 +3895,11 @@
       <c r="J82">
         <v>1800</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K82" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>90</v>
       </c>
@@ -3672,8 +3930,11 @@
       <c r="J83">
         <v>3800</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K83" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>115</v>
       </c>
@@ -3704,8 +3965,11 @@
       <c r="J84">
         <v>1300</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K84" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>116</v>
       </c>
@@ -3736,8 +4000,11 @@
       <c r="J85">
         <v>1300</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K85" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>117</v>
       </c>
@@ -3768,8 +4035,11 @@
       <c r="J86">
         <v>1300</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K86" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>118</v>
       </c>
@@ -3800,8 +4070,11 @@
       <c r="J87">
         <v>1300</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K87" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>119</v>
       </c>
@@ -3832,8 +4105,11 @@
       <c r="J88">
         <v>2800</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K88" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>120</v>
       </c>
@@ -3864,8 +4140,11 @@
       <c r="J89">
         <v>2800</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>121</v>
       </c>
@@ -3896,8 +4175,11 @@
       <c r="J90">
         <v>2800</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>122</v>
       </c>
@@ -3928,8 +4210,11 @@
       <c r="J91">
         <v>2800</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K91" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>110</v>
       </c>
@@ -3960,8 +4245,11 @@
       <c r="J92">
         <v>2100</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K92" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>112</v>
       </c>
@@ -3992,8 +4280,11 @@
       <c r="J93">
         <v>2100</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K93" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>111</v>
       </c>
@@ -4024,8 +4315,11 @@
       <c r="J94">
         <v>2100</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K94" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>114</v>
       </c>
@@ -4056,8 +4350,11 @@
       <c r="J95">
         <v>2100</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K95" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -4088,8 +4385,11 @@
       <c r="J96">
         <v>2800</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K96" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -4120,8 +4420,11 @@
       <c r="J97">
         <v>2800</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K97" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>113</v>
       </c>
@@ -4152,8 +4455,11 @@
       <c r="J98">
         <v>2800</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K98" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>109</v>
       </c>
@@ -4184,8 +4490,11 @@
       <c r="J99">
         <v>2800</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K99" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>123</v>
       </c>
@@ -4216,8 +4525,11 @@
       <c r="J100">
         <v>1800</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K100" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>124</v>
       </c>
@@ -4248,8 +4560,11 @@
       <c r="J101">
         <v>1800</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K101" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>125</v>
       </c>
@@ -4280,8 +4595,11 @@
       <c r="J102">
         <v>1800</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K102" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>126</v>
       </c>
@@ -4312,8 +4630,11 @@
       <c r="J103">
         <v>1800</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K103" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>127</v>
       </c>
@@ -4344,8 +4665,11 @@
       <c r="J104">
         <v>3050</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K104" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>128</v>
       </c>
@@ -4376,8 +4700,11 @@
       <c r="J105">
         <v>3050</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K105" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>129</v>
       </c>
@@ -4408,8 +4735,11 @@
       <c r="J106">
         <v>3050</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K106" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>130</v>
       </c>
@@ -4440,8 +4770,11 @@
       <c r="J107">
         <v>3050</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K107" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>91</v>
       </c>
@@ -4472,8 +4805,11 @@
       <c r="J108">
         <v>1800</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K108" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>92</v>
       </c>
@@ -4504,8 +4840,11 @@
       <c r="J109">
         <v>1800</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K109" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>93</v>
       </c>
@@ -4536,8 +4875,11 @@
       <c r="J110">
         <v>1800</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K110" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>98</v>
       </c>
@@ -4568,8 +4910,11 @@
       <c r="J111">
         <v>1800</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K111" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>94</v>
       </c>
@@ -4600,8 +4945,11 @@
       <c r="J112">
         <v>3200</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K112" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>97</v>
       </c>
@@ -4632,8 +4980,11 @@
       <c r="J113">
         <v>3200</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K113" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>95</v>
       </c>
@@ -4664,8 +5015,11 @@
       <c r="J114">
         <v>3200</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K114" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>96</v>
       </c>
@@ -4696,8 +5050,11 @@
       <c r="J115">
         <v>3200</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K115" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>131</v>
       </c>
@@ -4728,8 +5085,11 @@
       <c r="J116">
         <v>1800</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K116" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>133</v>
       </c>
@@ -4760,8 +5120,11 @@
       <c r="J117">
         <v>1800</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K117" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>132</v>
       </c>
@@ -4792,8 +5155,11 @@
       <c r="J118">
         <v>1800</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K118" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>134</v>
       </c>
@@ -4824,8 +5190,11 @@
       <c r="J119">
         <v>1800</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K119" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>135</v>
       </c>
@@ -4856,8 +5225,11 @@
       <c r="J120">
         <v>2600</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K120" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>136</v>
       </c>
@@ -4888,8 +5260,11 @@
       <c r="J121">
         <v>2600</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K121" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>137</v>
       </c>
@@ -4920,8 +5295,11 @@
       <c r="J122">
         <v>2600</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K122" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>138</v>
       </c>
@@ -4952,8 +5330,11 @@
       <c r="J123">
         <v>2600</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K123" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>99</v>
       </c>
@@ -4984,8 +5365,11 @@
       <c r="J124">
         <v>1800</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K124" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>101</v>
       </c>
@@ -5016,8 +5400,11 @@
       <c r="J125">
         <v>1800</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K125" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>100</v>
       </c>
@@ -5048,8 +5435,11 @@
       <c r="J126">
         <v>1800</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K126" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>102</v>
       </c>
@@ -5080,8 +5470,11 @@
       <c r="J127">
         <v>1800</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K127" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>103</v>
       </c>
@@ -5112,8 +5505,11 @@
       <c r="J128">
         <v>2500</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K128" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>104</v>
       </c>
@@ -5144,8 +5540,11 @@
       <c r="J129">
         <v>2500</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K129" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>105</v>
       </c>
@@ -5176,8 +5575,11 @@
       <c r="J130">
         <v>2500</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K130" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>106</v>
       </c>
@@ -5208,8 +5610,11 @@
       <c r="J131">
         <v>2500</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K131" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -5240,8 +5645,11 @@
       <c r="J132">
         <v>1800</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K132" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>140</v>
       </c>
@@ -5272,8 +5680,11 @@
       <c r="J133">
         <v>1800</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K133" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>143</v>
       </c>
@@ -5304,8 +5715,11 @@
       <c r="J134">
         <v>3200</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K134" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>144</v>
       </c>
@@ -5336,8 +5750,11 @@
       <c r="J135">
         <v>3200</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K135" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>141</v>
       </c>
@@ -5368,8 +5785,11 @@
       <c r="J136">
         <v>2000</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K136" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>142</v>
       </c>
@@ -5400,8 +5820,11 @@
       <c r="J137">
         <v>2000</v>
       </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K137" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>145</v>
       </c>
@@ -5432,8 +5855,11 @@
       <c r="J138">
         <v>3500</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K138" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>146</v>
       </c>
@@ -5464,8 +5890,11 @@
       <c r="J139">
         <v>3500</v>
       </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K139" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>147</v>
       </c>
@@ -5496,8 +5925,11 @@
       <c r="J140">
         <v>2100</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K140" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>148</v>
       </c>
@@ -5528,8 +5960,11 @@
       <c r="J141">
         <v>2100</v>
       </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K141" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>149</v>
       </c>
@@ -5560,8 +5995,11 @@
       <c r="J142">
         <v>2100</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K142" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>150</v>
       </c>
@@ -5592,8 +6030,11 @@
       <c r="J143">
         <v>2100</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K143" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>151</v>
       </c>
@@ -5624,8 +6065,11 @@
       <c r="J144">
         <v>2900</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K144" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>152</v>
       </c>
@@ -5656,8 +6100,11 @@
       <c r="J145">
         <v>2900</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K145" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>153</v>
       </c>
@@ -5688,8 +6135,11 @@
       <c r="J146">
         <v>2900</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K146" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>154</v>
       </c>
@@ -5720,8 +6170,11 @@
       <c r="J147">
         <v>2900</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K147" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>155</v>
       </c>
@@ -5752,8 +6205,11 @@
       <c r="J148">
         <v>2350</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K148" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>156</v>
       </c>
@@ -5784,8 +6240,11 @@
       <c r="J149">
         <v>2350</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K149" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>157</v>
       </c>
@@ -5816,8 +6275,11 @@
       <c r="J150">
         <v>2350</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K150" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>158</v>
       </c>
@@ -5848,8 +6310,11 @@
       <c r="J151">
         <v>2350</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K151" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>159</v>
       </c>
@@ -5880,8 +6345,11 @@
       <c r="J152">
         <v>2550</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K152" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>160</v>
       </c>
@@ -5912,8 +6380,11 @@
       <c r="J153">
         <v>2550</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K153" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>161</v>
       </c>
@@ -5944,8 +6415,11 @@
       <c r="J154">
         <v>2550</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K154" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>162</v>
       </c>
@@ -5976,8 +6450,11 @@
       <c r="J155">
         <v>2550</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K155" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>163</v>
       </c>
@@ -6008,8 +6485,11 @@
       <c r="J156">
         <v>2100</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K156" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>164</v>
       </c>
@@ -6040,8 +6520,11 @@
       <c r="J157">
         <v>2100</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K157" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>165</v>
       </c>
@@ -6072,8 +6555,11 @@
       <c r="J158">
         <v>2100</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K158" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -6104,8 +6590,11 @@
       <c r="J159">
         <v>2100</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K159" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>167</v>
       </c>
@@ -6136,8 +6625,11 @@
       <c r="J160">
         <v>2400</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K160" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>168</v>
       </c>
@@ -6168,8 +6660,11 @@
       <c r="J161">
         <v>2400</v>
       </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K161" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>169</v>
       </c>
@@ -6200,8 +6695,11 @@
       <c r="J162">
         <v>2400</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K162" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>170</v>
       </c>
@@ -6232,8 +6730,11 @@
       <c r="J163">
         <v>2400</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K163" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>171</v>
       </c>
@@ -6264,8 +6765,11 @@
       <c r="J164">
         <v>2100</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K164" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>172</v>
       </c>
@@ -6296,8 +6800,11 @@
       <c r="J165">
         <v>2100</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K165" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>173</v>
       </c>
@@ -6328,8 +6835,11 @@
       <c r="J166">
         <v>2600</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K166" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>174</v>
       </c>
@@ -6360,8 +6870,11 @@
       <c r="J167">
         <v>2600</v>
       </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K167" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>175</v>
       </c>
@@ -6392,8 +6905,11 @@
       <c r="J168">
         <v>2100</v>
       </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K168" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>176</v>
       </c>
@@ -6424,8 +6940,11 @@
       <c r="J169">
         <v>2100</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K169" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>177</v>
       </c>
@@ -6456,8 +6975,11 @@
       <c r="J170">
         <v>2600</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K170" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>178</v>
       </c>
@@ -6488,8 +7010,11 @@
       <c r="J171">
         <v>2600</v>
       </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K171" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>179</v>
       </c>
@@ -6520,8 +7045,11 @@
       <c r="J172">
         <v>2000</v>
       </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K172" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>180</v>
       </c>
@@ -6552,8 +7080,11 @@
       <c r="J173">
         <v>2000</v>
       </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K173" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>181</v>
       </c>
@@ -6584,8 +7115,11 @@
       <c r="J174">
         <v>3200</v>
       </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K174" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>182</v>
       </c>
@@ -6616,8 +7150,11 @@
       <c r="J175">
         <v>3200</v>
       </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K175" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>183</v>
       </c>
@@ -6648,8 +7185,11 @@
       <c r="J176">
         <v>2000</v>
       </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K176" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>184</v>
       </c>
@@ -6680,8 +7220,11 @@
       <c r="J177">
         <v>2000</v>
       </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K177" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>185</v>
       </c>
@@ -6712,8 +7255,11 @@
       <c r="J178">
         <v>3200</v>
       </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K178" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>186</v>
       </c>
@@ -6744,8 +7290,11 @@
       <c r="J179">
         <v>3200</v>
       </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K179" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>187</v>
       </c>
@@ -6776,8 +7325,11 @@
       <c r="J180">
         <v>2100</v>
       </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K180" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>188</v>
       </c>
@@ -6808,8 +7360,11 @@
       <c r="J181">
         <v>2100</v>
       </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K181" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>189</v>
       </c>
@@ -6840,8 +7395,11 @@
       <c r="J182">
         <v>2800</v>
       </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K182" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>190</v>
       </c>
@@ -6872,8 +7430,11 @@
       <c r="J183">
         <v>2800</v>
       </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K183" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>191</v>
       </c>
@@ -6904,8 +7465,11 @@
       <c r="J184">
         <v>2100</v>
       </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K184" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>192</v>
       </c>
@@ -6936,8 +7500,11 @@
       <c r="J185">
         <v>2100</v>
       </c>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K185" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>193</v>
       </c>
@@ -6968,8 +7535,11 @@
       <c r="J186">
         <v>2800</v>
       </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K186" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>194</v>
       </c>
@@ -7000,8 +7570,11 @@
       <c r="J187">
         <v>2800</v>
       </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K187" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>195</v>
       </c>
@@ -7032,8 +7605,11 @@
       <c r="J188">
         <v>1800</v>
       </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K188" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>196</v>
       </c>
@@ -7064,8 +7640,11 @@
       <c r="J189">
         <v>1800</v>
       </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K189" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>197</v>
       </c>
@@ -7096,8 +7675,11 @@
       <c r="J190">
         <v>2300</v>
       </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K190" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>198</v>
       </c>
@@ -7128,8 +7710,11 @@
       <c r="J191">
         <v>2300</v>
       </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K191" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>199</v>
       </c>
@@ -7160,8 +7745,11 @@
       <c r="J192">
         <v>1800</v>
       </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K192" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>200</v>
       </c>
@@ -7192,8 +7780,11 @@
       <c r="J193">
         <v>1800</v>
       </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K193" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>201</v>
       </c>
@@ -7224,8 +7815,11 @@
       <c r="J194">
         <v>2300</v>
       </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K194" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>202</v>
       </c>
@@ -7256,8 +7850,11 @@
       <c r="J195">
         <v>2300</v>
       </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K195" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -7288,8 +7885,11 @@
       <c r="J196">
         <v>1700</v>
       </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K196" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>204</v>
       </c>
@@ -7320,8 +7920,11 @@
       <c r="J197">
         <v>1700</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K197" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>205</v>
       </c>
@@ -7352,8 +7955,11 @@
       <c r="J198">
         <v>2150</v>
       </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K198" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>206</v>
       </c>
@@ -7384,8 +7990,11 @@
       <c r="J199">
         <v>2150</v>
       </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K199" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>207</v>
       </c>
@@ -7416,8 +8025,11 @@
       <c r="J200">
         <v>1700</v>
       </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K200" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>208</v>
       </c>
@@ -7448,8 +8060,11 @@
       <c r="J201">
         <v>1700</v>
       </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K201" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>209</v>
       </c>
@@ -7480,8 +8095,11 @@
       <c r="J202">
         <v>2150</v>
       </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K202" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>210</v>
       </c>
@@ -7512,8 +8130,11 @@
       <c r="J203">
         <v>2150</v>
       </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K203" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>211</v>
       </c>
@@ -7544,8 +8165,11 @@
       <c r="J204">
         <v>2100</v>
       </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K204" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>212</v>
       </c>
@@ -7576,8 +8200,11 @@
       <c r="J205">
         <v>2100</v>
       </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K205" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>213</v>
       </c>
@@ -7608,8 +8235,11 @@
       <c r="J206">
         <v>2100</v>
       </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K206" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>214</v>
       </c>
@@ -7640,8 +8270,11 @@
       <c r="J207">
         <v>2100</v>
       </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K207" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>215</v>
       </c>
@@ -7672,8 +8305,11 @@
       <c r="J208">
         <v>2200</v>
       </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K208" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>216</v>
       </c>
@@ -7704,8 +8340,11 @@
       <c r="J209">
         <v>2200</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K209" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>217</v>
       </c>
@@ -7736,8 +8375,11 @@
       <c r="J210">
         <v>2200</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K210" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>218</v>
       </c>
@@ -7768,8 +8410,11 @@
       <c r="J211">
         <v>2200</v>
       </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K211" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>219</v>
       </c>
@@ -7800,8 +8445,11 @@
       <c r="J212">
         <v>1500</v>
       </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K212" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>220</v>
       </c>
@@ -7831,6 +8479,9 @@
       </c>
       <c r="J213">
         <v>1125</v>
+      </c>
+      <c r="K213" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/public/Motors.xlsx
+++ b/public/Motors.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="228">
   <si>
     <t>name</t>
   </si>
@@ -702,6 +702,12 @@
   </si>
   <si>
     <t>https://smarta.ru/upload/iblock/fe7/ryifndfl23l64v8i1dvojliur5avjydh/EMMR_AS_A_1.png</t>
+  </si>
+  <si>
+    <t>mot_flangeSize</t>
+  </si>
+  <si>
+    <t>mot_wBrake</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K213"/>
+  <dimension ref="A1:M213"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
@@ -1029,7 +1035,7 @@
     <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1063,8 +1069,14 @@
       <c r="K1" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,14 @@
       <c r="K2" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2">
+        <v>40</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1133,8 +1151,14 @@
       <c r="K3" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3">
+        <v>40</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1168,8 +1192,14 @@
       <c r="K4" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4">
+        <v>60</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1233,14 @@
       <c r="K5" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5">
+        <v>60</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1238,8 +1274,14 @@
       <c r="K6" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6">
+        <v>60</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1273,8 +1315,14 @@
       <c r="K7" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7">
+        <v>60</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1308,8 +1356,14 @@
       <c r="K8" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8">
+        <v>80</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1343,8 +1397,14 @@
       <c r="K9" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9">
+        <v>80</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1378,8 +1438,14 @@
       <c r="K10" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10">
+        <v>80</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1413,8 +1479,14 @@
       <c r="K11" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11">
+        <v>80</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1448,8 +1520,14 @@
       <c r="K12" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12">
+        <v>130</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1483,8 +1561,14 @@
       <c r="K13" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13">
+        <v>130</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1518,8 +1602,14 @@
       <c r="K14" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14">
+        <v>130</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1553,8 +1643,14 @@
       <c r="K15" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15">
+        <v>130</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1588,8 +1684,14 @@
       <c r="K16" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16">
+        <v>130</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1623,8 +1725,14 @@
       <c r="K17" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17">
+        <v>130</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1658,8 +1766,14 @@
       <c r="K18" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18">
+        <v>130</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1807,14 @@
       <c r="K19" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19">
+        <v>130</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1728,8 +1848,14 @@
       <c r="K20" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20">
+        <v>130</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1763,8 +1889,14 @@
       <c r="K21" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21">
+        <v>130</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1798,8 +1930,14 @@
       <c r="K22" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <v>130</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1833,8 +1971,14 @@
       <c r="K23" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23">
+        <v>130</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1868,8 +2012,14 @@
       <c r="K24" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24">
+        <v>130</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1903,8 +2053,14 @@
       <c r="K25" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25">
+        <v>130</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1938,8 +2094,14 @@
       <c r="K26" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26">
+        <v>130</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1973,8 +2135,14 @@
       <c r="K27" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27">
+        <v>130</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -2008,8 +2176,14 @@
       <c r="K28" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28">
+        <v>180</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -2043,8 +2217,14 @@
       <c r="K29" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29">
+        <v>180</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -2078,8 +2258,14 @@
       <c r="K30" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30">
+        <v>180</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -2113,8 +2299,14 @@
       <c r="K31" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31">
+        <v>180</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -2148,8 +2340,14 @@
       <c r="K32" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32">
+        <v>180</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -2183,8 +2381,14 @@
       <c r="K33" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33">
+        <v>180</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -2218,8 +2422,14 @@
       <c r="K34" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34">
+        <v>180</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -2253,8 +2463,14 @@
       <c r="K35" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35">
+        <v>180</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2504,14 @@
       <c r="K36" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36">
+        <v>60</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -2323,8 +2545,14 @@
       <c r="K37" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37">
+        <v>60</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -2358,8 +2586,14 @@
       <c r="K38" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38">
+        <v>60</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -2393,8 +2627,14 @@
       <c r="K39" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39">
+        <v>60</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -2428,8 +2668,14 @@
       <c r="K40" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40">
+        <v>60</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -2463,8 +2709,14 @@
       <c r="K41" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41">
+        <v>60</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -2498,8 +2750,14 @@
       <c r="K42" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42">
+        <v>60</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -2533,8 +2791,14 @@
       <c r="K43" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43">
+        <v>60</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -2568,8 +2832,14 @@
       <c r="K44" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44">
+        <v>60</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -2603,8 +2873,14 @@
       <c r="K45" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45">
+        <v>60</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -2638,8 +2914,14 @@
       <c r="K46" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46">
+        <v>60</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -2673,8 +2955,14 @@
       <c r="K47" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47">
+        <v>60</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -2708,8 +2996,14 @@
       <c r="K48" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48">
+        <v>60</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -2743,8 +3037,14 @@
       <c r="K49" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49">
+        <v>60</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -2778,8 +3078,14 @@
       <c r="K50" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L50">
+        <v>60</v>
+      </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -2813,8 +3119,14 @@
       <c r="K51" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L51">
+        <v>60</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -2848,8 +3160,14 @@
       <c r="K52" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L52">
+        <v>60</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -2883,8 +3201,14 @@
       <c r="K53" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L53">
+        <v>60</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2918,8 +3242,14 @@
       <c r="K54" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L54">
+        <v>60</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -2953,8 +3283,14 @@
       <c r="K55" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L55">
+        <v>60</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -2988,8 +3324,14 @@
       <c r="K56" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L56">
+        <v>60</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -3023,8 +3365,14 @@
       <c r="K57" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L57">
+        <v>60</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -3058,8 +3406,14 @@
       <c r="K58" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L58">
+        <v>60</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -3093,8 +3447,14 @@
       <c r="K59" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L59">
+        <v>60</v>
+      </c>
+      <c r="M59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -3128,8 +3488,14 @@
       <c r="K60" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L60">
+        <v>80</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -3163,8 +3529,14 @@
       <c r="K61" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L61">
+        <v>80</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -3198,8 +3570,14 @@
       <c r="K62" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L62">
+        <v>80</v>
+      </c>
+      <c r="M62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -3233,8 +3611,14 @@
       <c r="K63" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L63">
+        <v>80</v>
+      </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -3268,8 +3652,14 @@
       <c r="K64" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L64">
+        <v>80</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -3303,8 +3693,14 @@
       <c r="K65" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L65">
+        <v>80</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -3338,8 +3734,14 @@
       <c r="K66" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L66">
+        <v>80</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -3373,8 +3775,14 @@
       <c r="K67" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L67">
+        <v>80</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -3408,8 +3816,14 @@
       <c r="K68" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L68">
+        <v>80</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -3443,8 +3857,14 @@
       <c r="K69" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L69">
+        <v>80</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -3478,8 +3898,14 @@
       <c r="K70" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L70">
+        <v>80</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -3513,8 +3939,14 @@
       <c r="K71" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L71">
+        <v>80</v>
+      </c>
+      <c r="M71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -3548,8 +3980,14 @@
       <c r="K72" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L72">
+        <v>80</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -3583,8 +4021,14 @@
       <c r="K73" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L73">
+        <v>80</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -3618,8 +4062,14 @@
       <c r="K74" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L74">
+        <v>80</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -3653,8 +4103,14 @@
       <c r="K75" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L75">
+        <v>80</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -3688,8 +4144,14 @@
       <c r="K76" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L76">
+        <v>80</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -3723,8 +4185,14 @@
       <c r="K77" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L77">
+        <v>80</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -3758,8 +4226,14 @@
       <c r="K78" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L78">
+        <v>80</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>86</v>
       </c>
@@ -3793,8 +4267,14 @@
       <c r="K79" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L79">
+        <v>80</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>87</v>
       </c>
@@ -3828,8 +4308,14 @@
       <c r="K80" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L80">
+        <v>80</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>88</v>
       </c>
@@ -3863,8 +4349,14 @@
       <c r="K81" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L81">
+        <v>80</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>89</v>
       </c>
@@ -3898,8 +4390,14 @@
       <c r="K82" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L82">
+        <v>80</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>90</v>
       </c>
@@ -3933,8 +4431,14 @@
       <c r="K83" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L83">
+        <v>80</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>115</v>
       </c>
@@ -3968,8 +4472,14 @@
       <c r="K84" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L84">
+        <v>90</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>116</v>
       </c>
@@ -4003,8 +4513,14 @@
       <c r="K85" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L85">
+        <v>90</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>117</v>
       </c>
@@ -4038,8 +4554,14 @@
       <c r="K86" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L86">
+        <v>90</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>118</v>
       </c>
@@ -4073,8 +4595,14 @@
       <c r="K87" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L87">
+        <v>90</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>119</v>
       </c>
@@ -4108,8 +4636,14 @@
       <c r="K88" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L88">
+        <v>90</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>120</v>
       </c>
@@ -4143,8 +4677,14 @@
       <c r="K89" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L89">
+        <v>90</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>121</v>
       </c>
@@ -4178,8 +4718,14 @@
       <c r="K90" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L90">
+        <v>90</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>122</v>
       </c>
@@ -4213,8 +4759,14 @@
       <c r="K91" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L91">
+        <v>90</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>110</v>
       </c>
@@ -4248,8 +4800,14 @@
       <c r="K92" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L92">
+        <v>90</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>112</v>
       </c>
@@ -4283,8 +4841,14 @@
       <c r="K93" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L93">
+        <v>90</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>111</v>
       </c>
@@ -4318,8 +4882,14 @@
       <c r="K94" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L94">
+        <v>90</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>114</v>
       </c>
@@ -4353,8 +4923,14 @@
       <c r="K95" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L95">
+        <v>90</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -4388,8 +4964,14 @@
       <c r="K96" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L96">
+        <v>90</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -4423,8 +5005,14 @@
       <c r="K97" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L97">
+        <v>90</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>113</v>
       </c>
@@ -4458,8 +5046,14 @@
       <c r="K98" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L98">
+        <v>90</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>109</v>
       </c>
@@ -4493,8 +5087,14 @@
       <c r="K99" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L99">
+        <v>90</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>123</v>
       </c>
@@ -4528,8 +5128,14 @@
       <c r="K100" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L100">
+        <v>90</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>124</v>
       </c>
@@ -4563,8 +5169,14 @@
       <c r="K101" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L101">
+        <v>90</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>125</v>
       </c>
@@ -4598,8 +5210,14 @@
       <c r="K102" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L102">
+        <v>90</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>126</v>
       </c>
@@ -4633,8 +5251,14 @@
       <c r="K103" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L103">
+        <v>90</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>127</v>
       </c>
@@ -4668,8 +5292,14 @@
       <c r="K104" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L104">
+        <v>90</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>128</v>
       </c>
@@ -4703,8 +5333,14 @@
       <c r="K105" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L105">
+        <v>90</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>129</v>
       </c>
@@ -4738,8 +5374,14 @@
       <c r="K106" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L106">
+        <v>90</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>130</v>
       </c>
@@ -4773,8 +5415,14 @@
       <c r="K107" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L107">
+        <v>90</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>91</v>
       </c>
@@ -4808,8 +5456,14 @@
       <c r="K108" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L108">
+        <v>90</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>92</v>
       </c>
@@ -4843,8 +5497,14 @@
       <c r="K109" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L109">
+        <v>90</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>93</v>
       </c>
@@ -4878,8 +5538,14 @@
       <c r="K110" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L110">
+        <v>90</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>98</v>
       </c>
@@ -4913,8 +5579,14 @@
       <c r="K111" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L111">
+        <v>90</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>94</v>
       </c>
@@ -4948,8 +5620,14 @@
       <c r="K112" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L112">
+        <v>90</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>97</v>
       </c>
@@ -4983,8 +5661,14 @@
       <c r="K113" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L113">
+        <v>90</v>
+      </c>
+      <c r="M113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>95</v>
       </c>
@@ -5018,8 +5702,14 @@
       <c r="K114" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L114">
+        <v>90</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>96</v>
       </c>
@@ -5053,8 +5743,14 @@
       <c r="K115" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L115">
+        <v>90</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>131</v>
       </c>
@@ -5088,8 +5784,14 @@
       <c r="K116" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L116">
+        <v>90</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>133</v>
       </c>
@@ -5123,8 +5825,14 @@
       <c r="K117" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L117">
+        <v>90</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>132</v>
       </c>
@@ -5158,8 +5866,14 @@
       <c r="K118" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L118">
+        <v>90</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>134</v>
       </c>
@@ -5193,8 +5907,14 @@
       <c r="K119" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L119">
+        <v>90</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>135</v>
       </c>
@@ -5228,8 +5948,14 @@
       <c r="K120" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L120">
+        <v>90</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>136</v>
       </c>
@@ -5263,8 +5989,14 @@
       <c r="K121" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L121">
+        <v>90</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>137</v>
       </c>
@@ -5298,8 +6030,14 @@
       <c r="K122" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L122">
+        <v>90</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>138</v>
       </c>
@@ -5333,8 +6071,14 @@
       <c r="K123" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L123">
+        <v>90</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>99</v>
       </c>
@@ -5368,8 +6112,14 @@
       <c r="K124" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L124">
+        <v>90</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>101</v>
       </c>
@@ -5403,8 +6153,14 @@
       <c r="K125" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L125">
+        <v>90</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>100</v>
       </c>
@@ -5438,8 +6194,14 @@
       <c r="K126" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L126">
+        <v>90</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>102</v>
       </c>
@@ -5473,8 +6235,14 @@
       <c r="K127" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L127">
+        <v>90</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>103</v>
       </c>
@@ -5508,8 +6276,14 @@
       <c r="K128" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L128">
+        <v>90</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>104</v>
       </c>
@@ -5543,8 +6317,14 @@
       <c r="K129" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L129">
+        <v>90</v>
+      </c>
+      <c r="M129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>105</v>
       </c>
@@ -5578,8 +6358,14 @@
       <c r="K130" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L130">
+        <v>90</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>106</v>
       </c>
@@ -5613,8 +6399,14 @@
       <c r="K131" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L131">
+        <v>90</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -5648,8 +6440,14 @@
       <c r="K132" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L132">
+        <v>100</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>140</v>
       </c>
@@ -5683,8 +6481,14 @@
       <c r="K133" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L133">
+        <v>100</v>
+      </c>
+      <c r="M133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>143</v>
       </c>
@@ -5718,8 +6522,14 @@
       <c r="K134" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L134">
+        <v>100</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>144</v>
       </c>
@@ -5753,8 +6563,14 @@
       <c r="K135" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L135">
+        <v>100</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>141</v>
       </c>
@@ -5788,8 +6604,14 @@
       <c r="K136" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L136">
+        <v>100</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>142</v>
       </c>
@@ -5823,8 +6645,14 @@
       <c r="K137" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L137">
+        <v>100</v>
+      </c>
+      <c r="M137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>145</v>
       </c>
@@ -5858,8 +6686,14 @@
       <c r="K138" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L138">
+        <v>100</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>146</v>
       </c>
@@ -5893,8 +6727,14 @@
       <c r="K139" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L139">
+        <v>100</v>
+      </c>
+      <c r="M139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>147</v>
       </c>
@@ -5928,8 +6768,14 @@
       <c r="K140" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L140">
+        <v>115</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>148</v>
       </c>
@@ -5963,8 +6809,14 @@
       <c r="K141" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L141">
+        <v>115</v>
+      </c>
+      <c r="M141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>149</v>
       </c>
@@ -5998,8 +6850,14 @@
       <c r="K142" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L142">
+        <v>115</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>150</v>
       </c>
@@ -6033,8 +6891,14 @@
       <c r="K143" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L143">
+        <v>115</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>151</v>
       </c>
@@ -6068,8 +6932,14 @@
       <c r="K144" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L144">
+        <v>115</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>152</v>
       </c>
@@ -6103,8 +6973,14 @@
       <c r="K145" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L145">
+        <v>115</v>
+      </c>
+      <c r="M145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>153</v>
       </c>
@@ -6138,8 +7014,14 @@
       <c r="K146" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L146">
+        <v>115</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>154</v>
       </c>
@@ -6173,8 +7055,14 @@
       <c r="K147" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L147">
+        <v>115</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>155</v>
       </c>
@@ -6208,8 +7096,14 @@
       <c r="K148" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L148">
+        <v>115</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>156</v>
       </c>
@@ -6243,8 +7137,14 @@
       <c r="K149" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L149">
+        <v>115</v>
+      </c>
+      <c r="M149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>157</v>
       </c>
@@ -6278,8 +7178,14 @@
       <c r="K150" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L150">
+        <v>115</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>158</v>
       </c>
@@ -6313,8 +7219,14 @@
       <c r="K151" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L151">
+        <v>115</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>159</v>
       </c>
@@ -6348,8 +7260,14 @@
       <c r="K152" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L152">
+        <v>115</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>160</v>
       </c>
@@ -6383,8 +7301,14 @@
       <c r="K153" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L153">
+        <v>115</v>
+      </c>
+      <c r="M153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>161</v>
       </c>
@@ -6418,8 +7342,14 @@
       <c r="K154" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L154">
+        <v>115</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>162</v>
       </c>
@@ -6453,8 +7383,14 @@
       <c r="K155" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L155">
+        <v>115</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>163</v>
       </c>
@@ -6488,8 +7424,14 @@
       <c r="K156" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L156">
+        <v>115</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>164</v>
       </c>
@@ -6523,8 +7465,14 @@
       <c r="K157" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L157">
+        <v>115</v>
+      </c>
+      <c r="M157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>165</v>
       </c>
@@ -6558,8 +7506,14 @@
       <c r="K158" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L158">
+        <v>115</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -6593,8 +7547,14 @@
       <c r="K159" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L159">
+        <v>115</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>167</v>
       </c>
@@ -6628,8 +7588,14 @@
       <c r="K160" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L160">
+        <v>115</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>168</v>
       </c>
@@ -6663,8 +7629,14 @@
       <c r="K161" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L161">
+        <v>115</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>169</v>
       </c>
@@ -6698,8 +7670,14 @@
       <c r="K162" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L162">
+        <v>115</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>170</v>
       </c>
@@ -6733,8 +7711,14 @@
       <c r="K163" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L163">
+        <v>115</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>171</v>
       </c>
@@ -6768,8 +7752,14 @@
       <c r="K164" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L164">
+        <v>115</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>172</v>
       </c>
@@ -6803,8 +7793,14 @@
       <c r="K165" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L165">
+        <v>115</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>173</v>
       </c>
@@ -6838,8 +7834,14 @@
       <c r="K166" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L166">
+        <v>115</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>174</v>
       </c>
@@ -6873,8 +7875,14 @@
       <c r="K167" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L167">
+        <v>115</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>175</v>
       </c>
@@ -6908,8 +7916,14 @@
       <c r="K168" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L168">
+        <v>115</v>
+      </c>
+      <c r="M168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>176</v>
       </c>
@@ -6943,8 +7957,14 @@
       <c r="K169" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L169">
+        <v>115</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>177</v>
       </c>
@@ -6978,8 +7998,14 @@
       <c r="K170" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L170">
+        <v>115</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>178</v>
       </c>
@@ -7013,8 +8039,14 @@
       <c r="K171" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L171">
+        <v>115</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>179</v>
       </c>
@@ -7048,8 +8080,14 @@
       <c r="K172" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L172">
+        <v>140</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>180</v>
       </c>
@@ -7083,8 +8121,14 @@
       <c r="K173" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L173">
+        <v>140</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>181</v>
       </c>
@@ -7118,8 +8162,14 @@
       <c r="K174" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L174">
+        <v>140</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>182</v>
       </c>
@@ -7153,8 +8203,14 @@
       <c r="K175" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L175">
+        <v>140</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>183</v>
       </c>
@@ -7188,8 +8244,14 @@
       <c r="K176" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L176">
+        <v>140</v>
+      </c>
+      <c r="M176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>184</v>
       </c>
@@ -7223,8 +8285,14 @@
       <c r="K177" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L177">
+        <v>140</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>185</v>
       </c>
@@ -7258,8 +8326,14 @@
       <c r="K178" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L178">
+        <v>140</v>
+      </c>
+      <c r="M178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>186</v>
       </c>
@@ -7293,8 +8367,14 @@
       <c r="K179" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L179">
+        <v>140</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>187</v>
       </c>
@@ -7328,8 +8408,14 @@
       <c r="K180" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L180">
+        <v>140</v>
+      </c>
+      <c r="M180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>188</v>
       </c>
@@ -7363,8 +8449,14 @@
       <c r="K181" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L181">
+        <v>140</v>
+      </c>
+      <c r="M181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>189</v>
       </c>
@@ -7398,8 +8490,14 @@
       <c r="K182" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L182">
+        <v>140</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>190</v>
       </c>
@@ -7433,8 +8531,14 @@
       <c r="K183" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L183">
+        <v>140</v>
+      </c>
+      <c r="M183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>191</v>
       </c>
@@ -7468,8 +8572,14 @@
       <c r="K184" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L184">
+        <v>140</v>
+      </c>
+      <c r="M184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>192</v>
       </c>
@@ -7503,8 +8613,14 @@
       <c r="K185" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L185">
+        <v>140</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>193</v>
       </c>
@@ -7538,8 +8654,14 @@
       <c r="K186" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L186">
+        <v>140</v>
+      </c>
+      <c r="M186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>194</v>
       </c>
@@ -7573,8 +8695,14 @@
       <c r="K187" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L187">
+        <v>140</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>195</v>
       </c>
@@ -7608,8 +8736,14 @@
       <c r="K188" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L188">
+        <v>140</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>196</v>
       </c>
@@ -7643,8 +8777,14 @@
       <c r="K189" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L189">
+        <v>140</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>197</v>
       </c>
@@ -7678,8 +8818,14 @@
       <c r="K190" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L190">
+        <v>140</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>198</v>
       </c>
@@ -7713,8 +8859,14 @@
       <c r="K191" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L191">
+        <v>140</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>199</v>
       </c>
@@ -7748,8 +8900,14 @@
       <c r="K192" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L192">
+        <v>140</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>200</v>
       </c>
@@ -7783,8 +8941,14 @@
       <c r="K193" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L193">
+        <v>140</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>201</v>
       </c>
@@ -7818,8 +8982,14 @@
       <c r="K194" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L194">
+        <v>140</v>
+      </c>
+      <c r="M194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>202</v>
       </c>
@@ -7853,8 +9023,14 @@
       <c r="K195" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L195">
+        <v>140</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -7888,8 +9064,14 @@
       <c r="K196" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L196">
+        <v>140</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>204</v>
       </c>
@@ -7923,8 +9105,14 @@
       <c r="K197" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L197">
+        <v>140</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>205</v>
       </c>
@@ -7958,8 +9146,14 @@
       <c r="K198" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L198">
+        <v>140</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>206</v>
       </c>
@@ -7993,8 +9187,14 @@
       <c r="K199" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L199">
+        <v>140</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>207</v>
       </c>
@@ -8028,8 +9228,14 @@
       <c r="K200" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L200">
+        <v>140</v>
+      </c>
+      <c r="M200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>208</v>
       </c>
@@ -8063,8 +9269,14 @@
       <c r="K201" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L201">
+        <v>140</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>209</v>
       </c>
@@ -8098,8 +9310,14 @@
       <c r="K202" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L202">
+        <v>140</v>
+      </c>
+      <c r="M202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>210</v>
       </c>
@@ -8133,8 +9351,14 @@
       <c r="K203" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L203">
+        <v>140</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>211</v>
       </c>
@@ -8168,8 +9392,14 @@
       <c r="K204" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L204">
+        <v>190</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>212</v>
       </c>
@@ -8203,8 +9433,14 @@
       <c r="K205" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L205">
+        <v>190</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>213</v>
       </c>
@@ -8238,8 +9474,14 @@
       <c r="K206" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L206">
+        <v>190</v>
+      </c>
+      <c r="M206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>214</v>
       </c>
@@ -8273,8 +9515,14 @@
       <c r="K207" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L207">
+        <v>190</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>215</v>
       </c>
@@ -8308,8 +9556,14 @@
       <c r="K208" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L208">
+        <v>190</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>216</v>
       </c>
@@ -8343,8 +9597,14 @@
       <c r="K209" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L209">
+        <v>190</v>
+      </c>
+      <c r="M209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>217</v>
       </c>
@@ -8378,8 +9638,14 @@
       <c r="K210" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L210">
+        <v>190</v>
+      </c>
+      <c r="M210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>218</v>
       </c>
@@ -8413,8 +9679,14 @@
       <c r="K211" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L211">
+        <v>190</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>219</v>
       </c>
@@ -8448,8 +9720,14 @@
       <c r="K212" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L212">
+        <v>190</v>
+      </c>
+      <c r="M212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>220</v>
       </c>
@@ -8482,6 +9760,12 @@
       </c>
       <c r="K213" t="s">
         <v>225</v>
+      </c>
+      <c r="L213">
+        <v>190</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/public/Motors.xlsx
+++ b/public/Motors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ru0nntr\Desktop\Прочее\Linear Motion Calculator\project_v0.96\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ru0nntr\Desktop\Прочее\Linear Motion Calculator\project_v0.97\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -695,19 +695,19 @@
     <t>mot_pic</t>
   </si>
   <si>
-    <t>https://smarta.ru/upload/iblock/7e6/s7ux3cbdzbpaw5w5ec0jax8tlb8ypfgv/EMMR_AS_BC_P_small_1.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/iblock/626/setjqkjevv8wqwc18qtalpo8e1dqg077/EMMR_AS_BC_big_1.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/iblock/fe7/ryifndfl23l64v8i1dvojliur5avjydh/EMMR_AS_A_1.png</t>
-  </si>
-  <si>
     <t>mot_flangeSize</t>
   </si>
   <si>
     <t>mot_wBrake</t>
+  </si>
+  <si>
+    <t>./pics/emmr-as-b_c-40_60_80.png</t>
+  </si>
+  <si>
+    <t>./pics/emmr-as-b_c-130_180.png</t>
+  </si>
+  <si>
+    <t>./pics/emmr-as-a.png</t>
   </si>
 </sst>
 </file>
@@ -1070,10 +1070,10 @@
         <v>222</v>
       </c>
       <c r="L1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="M1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1108,7 +1108,7 @@
         <v>3000</v>
       </c>
       <c r="K2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L2">
         <v>40</v>
@@ -1149,7 +1149,7 @@
         <v>3000</v>
       </c>
       <c r="K3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L3">
         <v>40</v>
@@ -1190,7 +1190,7 @@
         <v>3000</v>
       </c>
       <c r="K4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L4">
         <v>60</v>
@@ -1231,7 +1231,7 @@
         <v>3000</v>
       </c>
       <c r="K5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L5">
         <v>60</v>
@@ -1272,7 +1272,7 @@
         <v>3000</v>
       </c>
       <c r="K6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L6">
         <v>60</v>
@@ -1313,7 +1313,7 @@
         <v>3000</v>
       </c>
       <c r="K7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L7">
         <v>60</v>
@@ -1354,7 +1354,7 @@
         <v>3000</v>
       </c>
       <c r="K8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L8">
         <v>80</v>
@@ -1395,7 +1395,7 @@
         <v>3000</v>
       </c>
       <c r="K9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L9">
         <v>80</v>
@@ -1436,7 +1436,7 @@
         <v>3000</v>
       </c>
       <c r="K10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L10">
         <v>80</v>
@@ -1477,7 +1477,7 @@
         <v>3000</v>
       </c>
       <c r="K11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L11">
         <v>80</v>
@@ -1518,7 +1518,7 @@
         <v>1500</v>
       </c>
       <c r="K12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L12">
         <v>130</v>
@@ -1559,7 +1559,7 @@
         <v>1500</v>
       </c>
       <c r="K13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L13">
         <v>130</v>
@@ -1600,7 +1600,7 @@
         <v>1500</v>
       </c>
       <c r="K14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L14">
         <v>130</v>
@@ -1641,7 +1641,7 @@
         <v>1500</v>
       </c>
       <c r="K15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L15">
         <v>130</v>
@@ -1682,7 +1682,7 @@
         <v>1500</v>
       </c>
       <c r="K16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L16">
         <v>130</v>
@@ -1723,7 +1723,7 @@
         <v>1500</v>
       </c>
       <c r="K17" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L17">
         <v>130</v>
@@ -1764,7 +1764,7 @@
         <v>2500</v>
       </c>
       <c r="K18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L18">
         <v>130</v>
@@ -1805,7 +1805,7 @@
         <v>2500</v>
       </c>
       <c r="K19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L19">
         <v>130</v>
@@ -1846,7 +1846,7 @@
         <v>2500</v>
       </c>
       <c r="K20" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L20">
         <v>130</v>
@@ -1887,7 +1887,7 @@
         <v>2500</v>
       </c>
       <c r="K21" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L21">
         <v>130</v>
@@ -1928,7 +1928,7 @@
         <v>2500</v>
       </c>
       <c r="K22" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L22">
         <v>130</v>
@@ -1969,7 +1969,7 @@
         <v>2500</v>
       </c>
       <c r="K23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L23">
         <v>130</v>
@@ -2010,7 +2010,7 @@
         <v>2500</v>
       </c>
       <c r="K24" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L24">
         <v>130</v>
@@ -2051,7 +2051,7 @@
         <v>2500</v>
       </c>
       <c r="K25" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L25">
         <v>130</v>
@@ -2092,7 +2092,7 @@
         <v>2500</v>
       </c>
       <c r="K26" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L26">
         <v>130</v>
@@ -2133,7 +2133,7 @@
         <v>2500</v>
       </c>
       <c r="K27" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L27">
         <v>130</v>
@@ -2174,7 +2174,7 @@
         <v>1500</v>
       </c>
       <c r="K28" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L28">
         <v>180</v>
@@ -2215,7 +2215,7 @@
         <v>1500</v>
       </c>
       <c r="K29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L29">
         <v>180</v>
@@ -2256,7 +2256,7 @@
         <v>2000</v>
       </c>
       <c r="K30" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L30">
         <v>180</v>
@@ -2297,7 +2297,7 @@
         <v>2000</v>
       </c>
       <c r="K31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L31">
         <v>180</v>
@@ -2338,7 +2338,7 @@
         <v>1500</v>
       </c>
       <c r="K32" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L32">
         <v>180</v>
@@ -2379,7 +2379,7 @@
         <v>1500</v>
       </c>
       <c r="K33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L33">
         <v>180</v>
@@ -2420,7 +2420,7 @@
         <v>1500</v>
       </c>
       <c r="K34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L34">
         <v>180</v>
@@ -2461,7 +2461,7 @@
         <v>1500</v>
       </c>
       <c r="K35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L35">
         <v>180</v>
@@ -2502,7 +2502,7 @@
         <v>2000</v>
       </c>
       <c r="K36" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L36">
         <v>60</v>
@@ -2543,7 +2543,7 @@
         <v>4000</v>
       </c>
       <c r="K37" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L37">
         <v>60</v>
@@ -2584,7 +2584,7 @@
         <v>2000</v>
       </c>
       <c r="K38" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L38">
         <v>60</v>
@@ -2625,7 +2625,7 @@
         <v>4000</v>
       </c>
       <c r="K39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L39">
         <v>60</v>
@@ -2666,7 +2666,7 @@
         <v>5800</v>
       </c>
       <c r="K40" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L40">
         <v>60</v>
@@ -2707,7 +2707,7 @@
         <v>10000</v>
       </c>
       <c r="K41" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L41">
         <v>60</v>
@@ -2748,7 +2748,7 @@
         <v>5800</v>
       </c>
       <c r="K42" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L42">
         <v>60</v>
@@ -2789,7 +2789,7 @@
         <v>10000</v>
       </c>
       <c r="K43" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L43">
         <v>60</v>
@@ -2830,7 +2830,7 @@
         <v>1700</v>
       </c>
       <c r="K44" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L44">
         <v>60</v>
@@ -2871,7 +2871,7 @@
         <v>4400</v>
       </c>
       <c r="K45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L45">
         <v>60</v>
@@ -2912,7 +2912,7 @@
         <v>1700</v>
       </c>
       <c r="K46" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L46">
         <v>60</v>
@@ -2953,7 +2953,7 @@
         <v>4400</v>
       </c>
       <c r="K47" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L47">
         <v>60</v>
@@ -2994,7 +2994,7 @@
         <v>4600</v>
       </c>
       <c r="K48" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L48">
         <v>60</v>
@@ -3035,7 +3035,7 @@
         <v>5900</v>
       </c>
       <c r="K49" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L49">
         <v>60</v>
@@ -3076,7 +3076,7 @@
         <v>4600</v>
       </c>
       <c r="K50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L50">
         <v>60</v>
@@ -3117,7 +3117,7 @@
         <v>5900</v>
       </c>
       <c r="K51" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L51">
         <v>60</v>
@@ -3158,7 +3158,7 @@
         <v>1400</v>
       </c>
       <c r="K52" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L52">
         <v>60</v>
@@ -3199,7 +3199,7 @@
         <v>3000</v>
       </c>
       <c r="K53" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L53">
         <v>60</v>
@@ -3240,7 +3240,7 @@
         <v>1400</v>
       </c>
       <c r="K54" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L54">
         <v>60</v>
@@ -3281,7 +3281,7 @@
         <v>3000</v>
       </c>
       <c r="K55" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L55">
         <v>60</v>
@@ -3322,7 +3322,7 @@
         <v>4200</v>
       </c>
       <c r="K56" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L56">
         <v>60</v>
@@ -3363,7 +3363,7 @@
         <v>5900</v>
       </c>
       <c r="K57" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L57">
         <v>60</v>
@@ -3404,7 +3404,7 @@
         <v>4200</v>
       </c>
       <c r="K58" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L58">
         <v>60</v>
@@ -3445,7 +3445,7 @@
         <v>5900</v>
       </c>
       <c r="K59" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L59">
         <v>60</v>
@@ -3486,7 +3486,7 @@
         <v>1750</v>
       </c>
       <c r="K60" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L60">
         <v>80</v>
@@ -3527,7 +3527,7 @@
         <v>3100</v>
       </c>
       <c r="K61" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L61">
         <v>80</v>
@@ -3568,7 +3568,7 @@
         <v>1750</v>
       </c>
       <c r="K62" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L62">
         <v>80</v>
@@ -3609,7 +3609,7 @@
         <v>3100</v>
       </c>
       <c r="K63" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L63">
         <v>80</v>
@@ -3650,7 +3650,7 @@
         <v>1750</v>
       </c>
       <c r="K64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L64">
         <v>80</v>
@@ -3691,7 +3691,7 @@
         <v>5200</v>
       </c>
       <c r="K65" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L65">
         <v>80</v>
@@ -3732,7 +3732,7 @@
         <v>1750</v>
       </c>
       <c r="K66" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L66">
         <v>80</v>
@@ -3773,7 +3773,7 @@
         <v>5200</v>
       </c>
       <c r="K67" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L67">
         <v>80</v>
@@ -3814,7 +3814,7 @@
         <v>1600</v>
       </c>
       <c r="K68" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L68">
         <v>80</v>
@@ -3855,7 +3855,7 @@
         <v>3000</v>
       </c>
       <c r="K69" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L69">
         <v>80</v>
@@ -3896,7 +3896,7 @@
         <v>1600</v>
       </c>
       <c r="K70" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L70">
         <v>80</v>
@@ -3937,7 +3937,7 @@
         <v>3000</v>
       </c>
       <c r="K71" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L71">
         <v>80</v>
@@ -3978,7 +3978,7 @@
         <v>1600</v>
       </c>
       <c r="K72" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L72">
         <v>80</v>
@@ -4019,7 +4019,7 @@
         <v>3900</v>
       </c>
       <c r="K73" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L73">
         <v>80</v>
@@ -4060,7 +4060,7 @@
         <v>1600</v>
       </c>
       <c r="K74" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L74">
         <v>80</v>
@@ -4101,7 +4101,7 @@
         <v>3900</v>
       </c>
       <c r="K75" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L75">
         <v>80</v>
@@ -4142,7 +4142,7 @@
         <v>1600</v>
       </c>
       <c r="K76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L76">
         <v>80</v>
@@ -4183,7 +4183,7 @@
         <v>2450</v>
       </c>
       <c r="K77" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L77">
         <v>80</v>
@@ -4224,7 +4224,7 @@
         <v>1600</v>
       </c>
       <c r="K78" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L78">
         <v>80</v>
@@ -4265,7 +4265,7 @@
         <v>2450</v>
       </c>
       <c r="K79" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L79">
         <v>80</v>
@@ -4306,7 +4306,7 @@
         <v>1800</v>
       </c>
       <c r="K80" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L80">
         <v>80</v>
@@ -4347,7 +4347,7 @@
         <v>3800</v>
       </c>
       <c r="K81" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L81">
         <v>80</v>
@@ -4388,7 +4388,7 @@
         <v>1800</v>
       </c>
       <c r="K82" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L82">
         <v>80</v>
@@ -4429,7 +4429,7 @@
         <v>3800</v>
       </c>
       <c r="K83" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L83">
         <v>80</v>
@@ -4470,7 +4470,7 @@
         <v>1300</v>
       </c>
       <c r="K84" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L84">
         <v>90</v>
@@ -4511,7 +4511,7 @@
         <v>1300</v>
       </c>
       <c r="K85" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L85">
         <v>90</v>
@@ -4552,7 +4552,7 @@
         <v>1300</v>
       </c>
       <c r="K86" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L86">
         <v>90</v>
@@ -4593,7 +4593,7 @@
         <v>1300</v>
       </c>
       <c r="K87" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L87">
         <v>90</v>
@@ -4634,7 +4634,7 @@
         <v>2800</v>
       </c>
       <c r="K88" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L88">
         <v>90</v>
@@ -4675,7 +4675,7 @@
         <v>2800</v>
       </c>
       <c r="K89" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L89">
         <v>90</v>
@@ -4716,7 +4716,7 @@
         <v>2800</v>
       </c>
       <c r="K90" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L90">
         <v>90</v>
@@ -4757,7 +4757,7 @@
         <v>2800</v>
       </c>
       <c r="K91" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L91">
         <v>90</v>
@@ -4798,7 +4798,7 @@
         <v>2100</v>
       </c>
       <c r="K92" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L92">
         <v>90</v>
@@ -4839,7 +4839,7 @@
         <v>2100</v>
       </c>
       <c r="K93" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L93">
         <v>90</v>
@@ -4880,7 +4880,7 @@
         <v>2100</v>
       </c>
       <c r="K94" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L94">
         <v>90</v>
@@ -4921,7 +4921,7 @@
         <v>2100</v>
       </c>
       <c r="K95" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L95">
         <v>90</v>
@@ -4962,7 +4962,7 @@
         <v>2800</v>
       </c>
       <c r="K96" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L96">
         <v>90</v>
@@ -5003,7 +5003,7 @@
         <v>2800</v>
       </c>
       <c r="K97" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L97">
         <v>90</v>
@@ -5044,7 +5044,7 @@
         <v>2800</v>
       </c>
       <c r="K98" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L98">
         <v>90</v>
@@ -5085,7 +5085,7 @@
         <v>2800</v>
       </c>
       <c r="K99" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L99">
         <v>90</v>
@@ -5126,7 +5126,7 @@
         <v>1800</v>
       </c>
       <c r="K100" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L100">
         <v>90</v>
@@ -5167,7 +5167,7 @@
         <v>1800</v>
       </c>
       <c r="K101" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L101">
         <v>90</v>
@@ -5208,7 +5208,7 @@
         <v>1800</v>
       </c>
       <c r="K102" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L102">
         <v>90</v>
@@ -5249,7 +5249,7 @@
         <v>1800</v>
       </c>
       <c r="K103" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L103">
         <v>90</v>
@@ -5290,7 +5290,7 @@
         <v>3050</v>
       </c>
       <c r="K104" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L104">
         <v>90</v>
@@ -5331,7 +5331,7 @@
         <v>3050</v>
       </c>
       <c r="K105" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L105">
         <v>90</v>
@@ -5372,7 +5372,7 @@
         <v>3050</v>
       </c>
       <c r="K106" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L106">
         <v>90</v>
@@ -5413,7 +5413,7 @@
         <v>3050</v>
       </c>
       <c r="K107" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L107">
         <v>90</v>
@@ -5454,7 +5454,7 @@
         <v>1800</v>
       </c>
       <c r="K108" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L108">
         <v>90</v>
@@ -5495,7 +5495,7 @@
         <v>1800</v>
       </c>
       <c r="K109" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L109">
         <v>90</v>
@@ -5536,7 +5536,7 @@
         <v>1800</v>
       </c>
       <c r="K110" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L110">
         <v>90</v>
@@ -5577,7 +5577,7 @@
         <v>1800</v>
       </c>
       <c r="K111" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L111">
         <v>90</v>
@@ -5618,7 +5618,7 @@
         <v>3200</v>
       </c>
       <c r="K112" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L112">
         <v>90</v>
@@ -5659,7 +5659,7 @@
         <v>3200</v>
       </c>
       <c r="K113" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L113">
         <v>90</v>
@@ -5700,7 +5700,7 @@
         <v>3200</v>
       </c>
       <c r="K114" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L114">
         <v>90</v>
@@ -5741,7 +5741,7 @@
         <v>3200</v>
       </c>
       <c r="K115" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L115">
         <v>90</v>
@@ -5782,7 +5782,7 @@
         <v>1800</v>
       </c>
       <c r="K116" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L116">
         <v>90</v>
@@ -5823,7 +5823,7 @@
         <v>1800</v>
       </c>
       <c r="K117" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L117">
         <v>90</v>
@@ -5864,7 +5864,7 @@
         <v>1800</v>
       </c>
       <c r="K118" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L118">
         <v>90</v>
@@ -5905,7 +5905,7 @@
         <v>1800</v>
       </c>
       <c r="K119" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L119">
         <v>90</v>
@@ -5946,7 +5946,7 @@
         <v>2600</v>
       </c>
       <c r="K120" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L120">
         <v>90</v>
@@ -5987,7 +5987,7 @@
         <v>2600</v>
       </c>
       <c r="K121" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L121">
         <v>90</v>
@@ -6028,7 +6028,7 @@
         <v>2600</v>
       </c>
       <c r="K122" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L122">
         <v>90</v>
@@ -6069,7 +6069,7 @@
         <v>2600</v>
       </c>
       <c r="K123" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L123">
         <v>90</v>
@@ -6110,7 +6110,7 @@
         <v>1800</v>
       </c>
       <c r="K124" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L124">
         <v>90</v>
@@ -6151,7 +6151,7 @@
         <v>1800</v>
       </c>
       <c r="K125" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L125">
         <v>90</v>
@@ -6192,7 +6192,7 @@
         <v>1800</v>
       </c>
       <c r="K126" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L126">
         <v>90</v>
@@ -6233,7 +6233,7 @@
         <v>1800</v>
       </c>
       <c r="K127" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L127">
         <v>90</v>
@@ -6274,7 +6274,7 @@
         <v>2500</v>
       </c>
       <c r="K128" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L128">
         <v>90</v>
@@ -6315,7 +6315,7 @@
         <v>2500</v>
       </c>
       <c r="K129" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L129">
         <v>90</v>
@@ -6356,7 +6356,7 @@
         <v>2500</v>
       </c>
       <c r="K130" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L130">
         <v>90</v>
@@ -6397,7 +6397,7 @@
         <v>2500</v>
       </c>
       <c r="K131" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L131">
         <v>90</v>
@@ -6438,7 +6438,7 @@
         <v>1800</v>
       </c>
       <c r="K132" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L132">
         <v>100</v>
@@ -6479,7 +6479,7 @@
         <v>1800</v>
       </c>
       <c r="K133" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L133">
         <v>100</v>
@@ -6520,7 +6520,7 @@
         <v>3200</v>
       </c>
       <c r="K134" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L134">
         <v>100</v>
@@ -6561,7 +6561,7 @@
         <v>3200</v>
       </c>
       <c r="K135" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L135">
         <v>100</v>
@@ -6602,7 +6602,7 @@
         <v>2000</v>
       </c>
       <c r="K136" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L136">
         <v>100</v>
@@ -6643,7 +6643,7 @@
         <v>2000</v>
       </c>
       <c r="K137" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L137">
         <v>100</v>
@@ -6684,7 +6684,7 @@
         <v>3500</v>
       </c>
       <c r="K138" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L138">
         <v>100</v>
@@ -6725,7 +6725,7 @@
         <v>3500</v>
       </c>
       <c r="K139" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L139">
         <v>100</v>
@@ -6766,7 +6766,7 @@
         <v>2100</v>
       </c>
       <c r="K140" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L140">
         <v>115</v>
@@ -6807,7 +6807,7 @@
         <v>2100</v>
       </c>
       <c r="K141" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L141">
         <v>115</v>
@@ -6848,7 +6848,7 @@
         <v>2100</v>
       </c>
       <c r="K142" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L142">
         <v>115</v>
@@ -6889,7 +6889,7 @@
         <v>2100</v>
       </c>
       <c r="K143" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L143">
         <v>115</v>
@@ -6930,7 +6930,7 @@
         <v>2900</v>
       </c>
       <c r="K144" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L144">
         <v>115</v>
@@ -6971,7 +6971,7 @@
         <v>2900</v>
       </c>
       <c r="K145" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L145">
         <v>115</v>
@@ -7012,7 +7012,7 @@
         <v>2900</v>
       </c>
       <c r="K146" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L146">
         <v>115</v>
@@ -7053,7 +7053,7 @@
         <v>2900</v>
       </c>
       <c r="K147" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L147">
         <v>115</v>
@@ -7094,7 +7094,7 @@
         <v>2350</v>
       </c>
       <c r="K148" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L148">
         <v>115</v>
@@ -7135,7 +7135,7 @@
         <v>2350</v>
       </c>
       <c r="K149" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L149">
         <v>115</v>
@@ -7176,7 +7176,7 @@
         <v>2350</v>
       </c>
       <c r="K150" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L150">
         <v>115</v>
@@ -7217,7 +7217,7 @@
         <v>2350</v>
       </c>
       <c r="K151" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L151">
         <v>115</v>
@@ -7258,7 +7258,7 @@
         <v>2550</v>
       </c>
       <c r="K152" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L152">
         <v>115</v>
@@ -7299,7 +7299,7 @@
         <v>2550</v>
       </c>
       <c r="K153" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L153">
         <v>115</v>
@@ -7340,7 +7340,7 @@
         <v>2550</v>
       </c>
       <c r="K154" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L154">
         <v>115</v>
@@ -7381,7 +7381,7 @@
         <v>2550</v>
       </c>
       <c r="K155" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L155">
         <v>115</v>
@@ -7422,7 +7422,7 @@
         <v>2100</v>
       </c>
       <c r="K156" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L156">
         <v>115</v>
@@ -7463,7 +7463,7 @@
         <v>2100</v>
       </c>
       <c r="K157" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L157">
         <v>115</v>
@@ -7504,7 +7504,7 @@
         <v>2100</v>
       </c>
       <c r="K158" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L158">
         <v>115</v>
@@ -7545,7 +7545,7 @@
         <v>2100</v>
       </c>
       <c r="K159" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L159">
         <v>115</v>
@@ -7586,7 +7586,7 @@
         <v>2400</v>
       </c>
       <c r="K160" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L160">
         <v>115</v>
@@ -7627,7 +7627,7 @@
         <v>2400</v>
       </c>
       <c r="K161" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L161">
         <v>115</v>
@@ -7668,7 +7668,7 @@
         <v>2400</v>
       </c>
       <c r="K162" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L162">
         <v>115</v>
@@ -7709,7 +7709,7 @@
         <v>2400</v>
       </c>
       <c r="K163" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L163">
         <v>115</v>
@@ -7750,7 +7750,7 @@
         <v>2100</v>
       </c>
       <c r="K164" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L164">
         <v>115</v>
@@ -7791,7 +7791,7 @@
         <v>2100</v>
       </c>
       <c r="K165" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L165">
         <v>115</v>
@@ -7832,7 +7832,7 @@
         <v>2600</v>
       </c>
       <c r="K166" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L166">
         <v>115</v>
@@ -7873,7 +7873,7 @@
         <v>2600</v>
       </c>
       <c r="K167" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L167">
         <v>115</v>
@@ -7914,7 +7914,7 @@
         <v>2100</v>
       </c>
       <c r="K168" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L168">
         <v>115</v>
@@ -7955,7 +7955,7 @@
         <v>2100</v>
       </c>
       <c r="K169" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L169">
         <v>115</v>
@@ -7996,7 +7996,7 @@
         <v>2600</v>
       </c>
       <c r="K170" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L170">
         <v>115</v>
@@ -8037,7 +8037,7 @@
         <v>2600</v>
       </c>
       <c r="K171" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L171">
         <v>115</v>
@@ -8078,7 +8078,7 @@
         <v>2000</v>
       </c>
       <c r="K172" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L172">
         <v>140</v>
@@ -8119,7 +8119,7 @@
         <v>2000</v>
       </c>
       <c r="K173" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L173">
         <v>140</v>
@@ -8160,7 +8160,7 @@
         <v>3200</v>
       </c>
       <c r="K174" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L174">
         <v>140</v>
@@ -8201,7 +8201,7 @@
         <v>3200</v>
       </c>
       <c r="K175" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L175">
         <v>140</v>
@@ -8242,7 +8242,7 @@
         <v>2000</v>
       </c>
       <c r="K176" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L176">
         <v>140</v>
@@ -8283,7 +8283,7 @@
         <v>2000</v>
       </c>
       <c r="K177" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L177">
         <v>140</v>
@@ -8324,7 +8324,7 @@
         <v>3200</v>
       </c>
       <c r="K178" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L178">
         <v>140</v>
@@ -8365,7 +8365,7 @@
         <v>3200</v>
       </c>
       <c r="K179" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L179">
         <v>140</v>
@@ -8406,7 +8406,7 @@
         <v>2100</v>
       </c>
       <c r="K180" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L180">
         <v>140</v>
@@ -8447,7 +8447,7 @@
         <v>2100</v>
       </c>
       <c r="K181" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L181">
         <v>140</v>
@@ -8488,7 +8488,7 @@
         <v>2800</v>
       </c>
       <c r="K182" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L182">
         <v>140</v>
@@ -8529,7 +8529,7 @@
         <v>2800</v>
       </c>
       <c r="K183" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L183">
         <v>140</v>
@@ -8570,7 +8570,7 @@
         <v>2100</v>
       </c>
       <c r="K184" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L184">
         <v>140</v>
@@ -8611,7 +8611,7 @@
         <v>2100</v>
       </c>
       <c r="K185" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L185">
         <v>140</v>
@@ -8652,7 +8652,7 @@
         <v>2800</v>
       </c>
       <c r="K186" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L186">
         <v>140</v>
@@ -8693,7 +8693,7 @@
         <v>2800</v>
       </c>
       <c r="K187" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L187">
         <v>140</v>
@@ -8734,7 +8734,7 @@
         <v>1800</v>
       </c>
       <c r="K188" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L188">
         <v>140</v>
@@ -8775,7 +8775,7 @@
         <v>1800</v>
       </c>
       <c r="K189" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L189">
         <v>140</v>
@@ -8816,7 +8816,7 @@
         <v>2300</v>
       </c>
       <c r="K190" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L190">
         <v>140</v>
@@ -8857,7 +8857,7 @@
         <v>2300</v>
       </c>
       <c r="K191" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L191">
         <v>140</v>
@@ -8898,7 +8898,7 @@
         <v>1800</v>
       </c>
       <c r="K192" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L192">
         <v>140</v>
@@ -8939,7 +8939,7 @@
         <v>1800</v>
       </c>
       <c r="K193" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L193">
         <v>140</v>
@@ -8980,7 +8980,7 @@
         <v>2300</v>
       </c>
       <c r="K194" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L194">
         <v>140</v>
@@ -9021,7 +9021,7 @@
         <v>2300</v>
       </c>
       <c r="K195" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L195">
         <v>140</v>
@@ -9062,7 +9062,7 @@
         <v>1700</v>
       </c>
       <c r="K196" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L196">
         <v>140</v>
@@ -9103,7 +9103,7 @@
         <v>1700</v>
       </c>
       <c r="K197" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L197">
         <v>140</v>
@@ -9144,7 +9144,7 @@
         <v>2150</v>
       </c>
       <c r="K198" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L198">
         <v>140</v>
@@ -9185,7 +9185,7 @@
         <v>2150</v>
       </c>
       <c r="K199" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L199">
         <v>140</v>
@@ -9226,7 +9226,7 @@
         <v>1700</v>
       </c>
       <c r="K200" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L200">
         <v>140</v>
@@ -9267,7 +9267,7 @@
         <v>1700</v>
       </c>
       <c r="K201" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L201">
         <v>140</v>
@@ -9308,7 +9308,7 @@
         <v>2150</v>
       </c>
       <c r="K202" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L202">
         <v>140</v>
@@ -9349,7 +9349,7 @@
         <v>2150</v>
       </c>
       <c r="K203" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L203">
         <v>140</v>
@@ -9390,7 +9390,7 @@
         <v>2100</v>
       </c>
       <c r="K204" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L204">
         <v>190</v>
@@ -9431,7 +9431,7 @@
         <v>2100</v>
       </c>
       <c r="K205" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L205">
         <v>190</v>
@@ -9472,7 +9472,7 @@
         <v>2100</v>
       </c>
       <c r="K206" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L206">
         <v>190</v>
@@ -9513,7 +9513,7 @@
         <v>2100</v>
       </c>
       <c r="K207" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L207">
         <v>190</v>
@@ -9554,7 +9554,7 @@
         <v>2200</v>
       </c>
       <c r="K208" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L208">
         <v>190</v>
@@ -9595,7 +9595,7 @@
         <v>2200</v>
       </c>
       <c r="K209" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L209">
         <v>190</v>
@@ -9636,7 +9636,7 @@
         <v>2200</v>
       </c>
       <c r="K210" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L210">
         <v>190</v>
@@ -9677,7 +9677,7 @@
         <v>2200</v>
       </c>
       <c r="K211" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L211">
         <v>190</v>
@@ -9718,7 +9718,7 @@
         <v>1500</v>
       </c>
       <c r="K212" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L212">
         <v>190</v>
@@ -9759,7 +9759,7 @@
         <v>1125</v>
       </c>
       <c r="K213" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L213">
         <v>190</v>
